--- a/tests/test_01/build_files/Test_1_layout.xlsx
+++ b/tests/test_01/build_files/Test_1_layout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/killedar_email_sc_edu/Documents/Documents/GitHub/Dataset-LPBF-Thin-Wall-and-Cube-Thermal-Optical-Monitoring/build_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Dataset-LPBF-Thin-Wall-and-Cube-Thermal-Optical-Monitoring\tests\test_01\build_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_F25DC773A252ABDACC104816C91C694E5ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11FC2F51-C362-4E05-AF0E-72237324C774}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75742ADE-D947-433E-BE36-613D6A872DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,13 +27,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
-    <t>position</t>
-  </si>
-  <si>
     <t>wall thinkness (mm)</t>
   </si>
   <si>
     <t>Cube width (mm)</t>
+  </si>
+  <si>
+    <t>position (1 -starting at left)</t>
   </si>
 </sst>
 </file>
@@ -641,22 +641,24 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">

--- a/tests/test_01/build_files/Test_1_layout.xlsx
+++ b/tests/test_01/build_files/Test_1_layout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Dataset-LPBF-Thin-Wall-and-Cube-Thermal-Optical-Monitoring\tests\test_01\build_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75742ADE-D947-433E-BE36-613D6A872DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75E58C3-5347-4FC5-A55D-CF3EB3219E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,16 +188,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>484107</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>39713</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>245166</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>52967</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>196006</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>39455</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>427919</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>57449</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -220,8 +220,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4698920" y="1111276"/>
-          <a:ext cx="5784086" cy="3035835"/>
+          <a:off x="7666383" y="1537210"/>
+          <a:ext cx="4449953" cy="2416378"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -232,16 +232,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>87631</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>253283</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>5953</xdr:rowOff>
+      <xdr:rowOff>78840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>531734</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>87786</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>41672</xdr:rowOff>
+      <xdr:rowOff>114559</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -256,8 +256,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5516881" y="2684859"/>
-          <a:ext cx="444103" cy="214313"/>
+          <a:off x="8284100" y="2861797"/>
+          <a:ext cx="444103" cy="221249"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/tests/test_01/build_files/Test_1_layout.xlsx
+++ b/tests/test_01/build_files/Test_1_layout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Dataset-LPBF-Thin-Wall-and-Cube-Thermal-Optical-Monitoring\tests\test_01\build_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75E58C3-5347-4FC5-A55D-CF3EB3219E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BC93FA-FB6E-408D-B70D-2F6AD557F8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -149,7 +149,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>125730</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -188,67 +188,84 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>245166</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>52967</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>315670</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>46728</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>427919</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>57449</xdr:rowOff>
+      <xdr:colOff>517375</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>113964</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1DF96F0-BB58-4672-FF97-3F8777B321F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86B5DDAC-D4C4-7FB7-F4C2-82335DAD7DC2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="4066" t="15654" r="11966" b="20615"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7666383" y="1537210"/>
-          <a:ext cx="4449953" cy="2416378"/>
+          <a:off x="3823111" y="2198257"/>
+          <a:ext cx="8348382" cy="4011707"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>253283</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>78840</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>41943</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>46141</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>87786</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>114559</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>504599</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>81860</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
+        <xdr:cNvPr id="6" name="TextBox 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8301BAEC-E423-4118-7A04-56B30926CE6C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EEA8B8B-BD2A-4699-B0F0-E9E2B814770A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -256,8 +273,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8284100" y="2861797"/>
-          <a:ext cx="444103" cy="221249"/>
+          <a:off x="6250002" y="4887082"/>
+          <a:ext cx="462656" cy="215013"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -303,23 +320,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>523876</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>109061</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>143344</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>18202</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>448388</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>67855</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>56713</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 3">
+        <xdr:cNvPr id="7" name="TextBox 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD44CED3-487F-A5DD-5CC7-061F9E77501F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27DCA34E-83D5-4513-AE64-80CC98E4D69A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -327,8 +344,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8989220" y="2252186"/>
-          <a:ext cx="531731" cy="212408"/>
+          <a:off x="9376991" y="2886908"/>
+          <a:ext cx="529629" cy="217805"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
